--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_117_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_117_R12.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8535</v>
+        <v>6.0202</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2484</v>
+        <v>4.0808</v>
       </c>
       <c r="F2" t="n">
-        <v>1.605</v>
+        <v>1.9394</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8225</v>
+        <v>2.0793</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2435</v>
+        <v>0.9617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.579</v>
+        <v>1.1176</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1763</v>
+        <v>1.8575</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3298</v>
+        <v>0.8907</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8465</v>
+        <v>0.9669</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3538</v>
+        <v>0.2218</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0862</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2676</v>
+        <v>0.1507</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>4.0156</v>
+        <v>-0.7549</v>
       </c>
       <c r="T2" t="n">
-        <v>5.0721</v>
+        <v>0.0788</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0565</v>
+        <v>-0.8338</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5917</v>
+        <v>5.2385</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6522</v>
+        <v>3.331</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9394</v>
+        <v>1.9075</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0793</v>
+        <v>0.8225</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9617</v>
+        <v>0.2435</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1176</v>
+        <v>0.579</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8575</v>
+        <v>1.1763</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8907</v>
+        <v>0.3298</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9669</v>
+        <v>0.8465</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2218</v>
+        <v>-0.3538</v>
       </c>
       <c r="N3" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.0862</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1507</v>
+        <v>-0.2676</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1835</v>
+        <v>1.4007</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3497</v>
+        <v>2.1548</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8338</v>
+        <v>-0.7541</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3624</v>
+        <v>2.5479</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9741</v>
+        <v>2.5357</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6117</v>
+        <v>0.0122</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3951</v>
+        <v>1.7412</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7695</v>
+        <v>0.0181</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6256</v>
+        <v>1.7232</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1135</v>
+        <v>2.4059</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2115</v>
+        <v>0.0504</v>
       </c>
       <c r="L4" t="n">
-        <v>1.325</v>
+        <v>2.3555</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5086</v>
+        <v>-0.6647</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5581</v>
+        <v>-0.0323</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9505</v>
+        <v>-0.6323</v>
       </c>
       <c r="P4" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7059</v>
+        <v>0.0206</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2007</v>
+        <v>0.1298</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5052</v>
+        <v>-0.1092</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8197</v>
+        <v>-0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2949</v>
+        <v>2.5012</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1819</v>
+        <v>2.0369</v>
       </c>
       <c r="F5" t="n">
-        <v>0.113</v>
+        <v>0.4643</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7412</v>
+        <v>0.2249</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0181</v>
+        <v>-2.3013</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7232</v>
+        <v>2.5262</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4059</v>
+        <v>1.1683</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0504</v>
+        <v>-2.2043</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3555</v>
+        <v>3.3726</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6647</v>
+        <v>-0.9434</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0323</v>
+        <v>-0.097</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6323</v>
+        <v>-0.8464</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>3.2473</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2324</v>
+        <v>0.4413</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.224</v>
+        <v>0.6726</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0083</v>
+        <v>-0.2313</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>-0.2525</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.3558</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6764</v>
+        <v>1.321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.708</v>
+        <v>0.7861</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9684</v>
+        <v>0.5349</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2249</v>
+        <v>-1.2888</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3013</v>
+        <v>-0.3218</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5262</v>
+        <v>-0.967</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1683</v>
+        <v>-0.0665</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2043</v>
+        <v>0.0574</v>
       </c>
       <c r="L6" t="n">
-        <v>3.3726</v>
+        <v>-0.1239</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9434</v>
+        <v>-1.2223</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.097</v>
+        <v>-0.3792</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8464</v>
+        <v>-0.8431</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2473</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3835</v>
+        <v>0.3932</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6563</v>
+        <v>0.4916</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2728</v>
+        <v>-0.0984</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2525</v>
+        <v>2.6805</v>
       </c>
       <c r="W6" t="n">
-        <v>1.3558</v>
+        <v>2.6805</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5386</v>
+        <v>0.7913</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0037</v>
+        <v>1.722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5349</v>
+        <v>-0.9307</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2888</v>
+        <v>1.69</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3218</v>
+        <v>0.5558</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.967</v>
+        <v>1.1342</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0665</v>
+        <v>3.6554</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0574</v>
+        <v>1.1462</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1239</v>
+        <v>2.5091</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2223</v>
+        <v>-1.9654</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3792</v>
+        <v>-0.5904</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8431</v>
+        <v>-1.375</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3892</v>
+        <v>-0.5739</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2908</v>
+        <v>0.1026</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0984</v>
+        <v>-0.6765</v>
       </c>
       <c r="V7" t="n">
-        <v>2.6805</v>
+        <v>-0.7886</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6805</v>
+        <v>0.2836</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6617</v>
+        <v>0.6748</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6723</v>
+        <v>1.6898</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.334</v>
+        <v>-1.015</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>-1.3951</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5558</v>
+        <v>-0.7695</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1342</v>
+        <v>-0.6256</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6554</v>
+        <v>1.1135</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1462</v>
+        <v>-0.2115</v>
       </c>
       <c r="L8" t="n">
-        <v>2.5091</v>
+        <v>1.325</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9654</v>
+        <v>-2.5086</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5904</v>
+        <v>-0.5581</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.375</v>
+        <v>-1.9505</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0269</v>
+        <v>1.0183</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9471000000000001</v>
+        <v>0.9164</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0798</v>
+        <v>0.1019</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7886</v>
+        <v>0.8197</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2836</v>
+        <v>0.8197</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8967000000000001</v>
+        <v>-0.3942</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4148</v>
+        <v>0.6822</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3116</v>
+        <v>-1.0763</v>
       </c>
       <c r="G9" t="n">
         <v>-2.5728</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4441</v>
+        <v>0.9467</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6844</v>
+        <v>0.9517</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2403</v>
+        <v>-0.005</v>
       </c>
       <c r="V9" t="n">
         <v>0.5361</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2595</v>
+        <v>-2.9051</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4837</v>
+        <v>-2.4654</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7758</v>
+        <v>-0.4397</v>
       </c>
       <c r="G10" t="n">
         <v>-0.479</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5332</v>
+        <v>-0.1788</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7231</v>
+        <v>0.2952</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8101</v>
+        <v>-0.474</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0187</v>
+        <v>-4.1945</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8236</v>
+        <v>-3.7306</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.195</v>
+        <v>-0.4639</v>
       </c>
       <c r="G11" t="n">
         <v>-5.8078</v>
@@ -1312,13 +1312,13 @@
         <v>2.5515</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1387</v>
+        <v>-0.3145</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9471000000000001</v>
+        <v>0.1458</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1915</v>
+        <v>-0.4604</v>
       </c>
       <c r="V11" t="n">
         <v>0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.4809</v>
+        <v>11.6011</v>
       </c>
       <c r="E12" t="n">
-        <v>9.548100000000005</v>
+        <v>10.6685</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9326000000000001</v>
+        <v>0.9326999999999996</v>
       </c>
       <c r="G12" t="n">
         <v>-4.985600000000001</v>
@@ -1381,7 +1381,7 @@
         <v>-10.3042</v>
       </c>
       <c r="P12" t="n">
-        <v>8.118500000000001</v>
+        <v>8.118499999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.9172</v>
@@ -1390,13 +1390,13 @@
         <v>22.0354</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2782</v>
+        <v>2.398700000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.819100000000001</v>
+        <v>5.939300000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.5407</v>
+        <v>-3.5408</v>
       </c>
       <c r="V12" t="n">
         <v>6.07</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9904</v>
+        <v>6.3494</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9896</v>
+        <v>7.9332</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9992</v>
+        <v>-1.5838</v>
       </c>
       <c r="G13" t="n">
         <v>8.766500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.9773</v>
+        <v>-0.6183</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8136</v>
+        <v>0.13</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1637</v>
+        <v>-0.7483</v>
       </c>
       <c r="V13" t="n">
         <v>2.1444</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.089</v>
+        <v>1.8463</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6596</v>
+        <v>3.0646</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4294</v>
+        <v>-1.2182</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5944</v>
+        <v>2.9943</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1092</v>
+        <v>1.4585</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4852</v>
+        <v>1.5358</v>
       </c>
       <c r="J14" t="n">
-        <v>3.052</v>
+        <v>4.4128</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3527</v>
+        <v>0.612</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6993</v>
+        <v>3.8008</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4576</v>
+        <v>-1.4185</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2435</v>
+        <v>0.8466</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.214</v>
+        <v>-2.2651</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.4793</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1362</v>
+        <v>-0.5397</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9451</v>
+        <v>0.0435</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1911</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4172</v>
+        <v>1.489</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3012</v>
+        <v>0.8903</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.884</v>
+        <v>0.5987</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9287</v>
+        <v>2.5944</v>
       </c>
       <c r="H15" t="n">
-        <v>0.065</v>
+        <v>2.1092</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9937</v>
+        <v>0.4852</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5292</v>
+        <v>3.052</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6351</v>
+        <v>2.3527</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1643</v>
+        <v>0.6993</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.458</v>
+        <v>-0.4576</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7000999999999999</v>
+        <v>-0.2435</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1581</v>
+        <v>-0.214</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1598</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0058</v>
+        <v>1.5362</v>
       </c>
       <c r="T15" t="n">
-        <v>3.0039</v>
+        <v>1.1758</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9981</v>
+        <v>0.3605</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.8197</v>
+        <v>0.1418</v>
       </c>
       <c r="W15" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="X15" t="n">
         <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.8197</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7461</v>
+        <v>1.2457</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3569</v>
+        <v>1.2639</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6108</v>
+        <v>-0.0182</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9943</v>
+        <v>-0.7557</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4585</v>
+        <v>2.587</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5358</v>
+        <v>-3.3427</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4128</v>
+        <v>0.759</v>
       </c>
       <c r="K16" t="n">
-        <v>0.612</v>
+        <v>1.4151</v>
       </c>
       <c r="L16" t="n">
-        <v>3.8008</v>
+        <v>-0.6561</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4185</v>
+        <v>-1.5147</v>
       </c>
       <c r="N16" t="n">
-        <v>0.8466</v>
+        <v>1.1719</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.2651</v>
+        <v>-2.6866</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6399</v>
+        <v>-0.3903</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6642</v>
+        <v>0.2008</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9757</v>
+        <v>-0.5911</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W16" t="n">
+        <v>0.5361</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>J. AYAYI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5944</v>
+        <v>-0.046</v>
       </c>
       <c r="E17" t="n">
-        <v>1.028</v>
+        <v>0.3225</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4336</v>
+        <v>-0.3685</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7557</v>
+        <v>0.0901</v>
       </c>
       <c r="H17" t="n">
-        <v>2.587</v>
+        <v>0.1069</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.3427</v>
+        <v>-0.0167</v>
       </c>
       <c r="J17" t="n">
-        <v>0.759</v>
+        <v>0.3225</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4151</v>
+        <v>0.2857</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6561</v>
+        <v>0.0368</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5147</v>
+        <v>-0.2323</v>
       </c>
       <c r="N17" t="n">
-        <v>1.1719</v>
+        <v>-0.1788</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.6866</v>
+        <v>-0.0535</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0416</v>
+        <v>0.168</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0351</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0064</v>
+        <v>0.168</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>-0.5361</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. AYAYI</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1468</v>
+        <v>-0.3292</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3225</v>
+        <v>1.5319</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4693</v>
+        <v>-1.8612</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0901</v>
+        <v>-0.9287</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1069</v>
+        <v>0.065</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0167</v>
+        <v>-0.9937</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3225</v>
+        <v>0.5292</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2857</v>
+        <v>-0.6351</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>1.1643</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2323</v>
+        <v>-1.458</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1788</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0535</v>
+        <v>-2.1581</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0672</v>
+        <v>0.2594</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.2346</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0672</v>
+        <v>-0.9752</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>-0.8197</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5361</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. BAKO</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0134</v>
+        <v>-0.6655</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2994</v>
+        <v>-2.0213</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.714</v>
+        <v>1.3557</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0136</v>
+        <v>-1.886</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4418</v>
+        <v>0.4395</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4282</v>
+        <v>-2.3255</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3163</v>
+        <v>-1.9861</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0587</v>
+        <v>0.3361</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2576</v>
+        <v>-2.3222</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6972</v>
+        <v>0.1001</v>
       </c>
       <c r="N19" t="n">
-        <v>1.3831</v>
+        <v>0.1034</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6859</v>
+        <v>-0.0033</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8852</v>
+        <v>0.2025</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.224</v>
+        <v>-0.0351</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6611</v>
+        <v>0.2377</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>I. BAKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2442</v>
+        <v>-0.9963</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0927</v>
+        <v>-0.1814</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1515</v>
+        <v>-0.8148</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9098000000000001</v>
+        <v>2.0136</v>
       </c>
       <c r="H20" t="n">
-        <v>0.365</v>
+        <v>2.4418</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2747</v>
+        <v>-0.4282</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0379</v>
+        <v>1.3163</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8907</v>
+        <v>1.0587</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1472</v>
+        <v>0.2576</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9477</v>
+        <v>0.6972</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5256999999999999</v>
+        <v>1.3831</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.422</v>
+        <v>-0.6859</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8975</v>
+        <v>-0.8681</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1889</v>
+        <v>-0.1061</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7086</v>
+        <v>-0.762</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6535</v>
+        <v>-1.4566</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4931</v>
+        <v>-1.0927</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8396</v>
+        <v>-0.3639</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.886</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4395</v>
+        <v>0.365</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3255</v>
+        <v>-1.2747</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.9861</v>
+        <v>1.0379</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3361</v>
+        <v>0.8907</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.3222</v>
+        <v>0.1472</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1001</v>
+        <v>-1.9477</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1034</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0033</v>
+        <v>-1.422</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7855</v>
+        <v>0.6851</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.507</v>
+        <v>0.1889</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2785</v>
+        <v>0.4962</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3464</v>
+        <v>-3.6389</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9343</v>
+        <v>-1.5572</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5879</v>
+        <v>-2.0817</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.523</v>
+        <v>-0.5898</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.4129</v>
+        <v>-1.587</v>
       </c>
       <c r="I22" t="n">
-        <v>0.89</v>
+        <v>0.9971</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.8658</v>
+        <v>-0.4684</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.0229</v>
+        <v>-1.5223</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1571</v>
+        <v>1.0539</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3428</v>
+        <v>-0.1215</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.39</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7328</v>
+        <v>-0.0568</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.9432</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8672</v>
+        <v>0.3273</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4288</v>
+        <v>0.0709</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4384</v>
+        <v>0.2563</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2525</v>
+        <v>-2.6805</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1107</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6326</v>
+        <v>-4.5531</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.911</v>
+        <v>-6.0522</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7216</v>
+        <v>1.4991</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5898</v>
+        <v>-1.523</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.587</v>
+        <v>-2.4129</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9971</v>
+        <v>0.89</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4684</v>
+        <v>-1.8658</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5223</v>
+        <v>-2.0229</v>
       </c>
       <c r="L23" t="n">
-        <v>1.0539</v>
+        <v>0.1571</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1215</v>
+        <v>0.3428</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.39</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0568</v>
+        <v>0.7328</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6959</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6664</v>
+        <v>0.6605</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2829</v>
+        <v>0.3108</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3835</v>
+        <v>0.3497</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.6805</v>
+        <v>0.2525</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6805</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.2811</v>
+        <v>-6.5803</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.8599</v>
+        <v>-5.0343</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4211</v>
+        <v>-1.546</v>
       </c>
       <c r="G24" t="n">
         <v>-4.8803</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2564</v>
+        <v>0.4443</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4991</v>
+        <v>0.3266</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7573</v>
+        <v>0.1177</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1444</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.4809</v>
+        <v>-7.3355</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.932599999999999</v>
+        <v>-0.9327000000000014</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.548199999999998</v>
+        <v>-6.4028</v>
       </c>
       <c r="G25" t="n">
-        <v>4.985600000000002</v>
+        <v>4.985599999999998</v>
       </c>
       <c r="H25" t="n">
         <v>6.290800000000001</v>
@@ -2380,7 +2380,7 @@
         <v>13.5256</v>
       </c>
       <c r="K25" t="n">
-        <v>3.221600000000001</v>
+        <v>3.2216</v>
       </c>
       <c r="L25" t="n">
         <v>10.304</v>
@@ -2404,19 +2404,19 @@
         <v>13.9174</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2784</v>
+        <v>1.8669</v>
       </c>
       <c r="T25" t="n">
-        <v>3.5408</v>
+        <v>3.5407</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.819</v>
+        <v>-1.6737</v>
       </c>
       <c r="V25" t="n">
         <v>-6.07</v>
       </c>
       <c r="W25" t="n">
-        <v>4.0363</v>
+        <v>4.036300000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-10.1063</v>
